--- a/IEF_Home/UploadedFiles/3_MC_VehicleArchetypes_TABLE_Sample_Errors.xlsx
+++ b/IEF_Home/UploadedFiles/3_MC_VehicleArchetypes_TABLE_Sample_Errors.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20416"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F600CD-D5AD-46A8-9417-A0B8DC8962CD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3141EB-62B2-4A39-8A2F-6A6ECD4FAE53}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25596" windowHeight="15996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25596" windowHeight="15996" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="10" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="384">
   <si>
     <t>Format_Version</t>
   </si>
@@ -510,9 +510,6 @@
     <t>HFCEV minivan/SUV lightweight</t>
   </si>
   <si>
-    <t>ICEV-g_Microcar_Conventional design</t>
-  </si>
-  <si>
     <t>ICEV-g_Passenger car_Conventional design</t>
   </si>
   <si>
@@ -1180,6 +1177,15 @@
   </si>
   <si>
     <t>Different data sources</t>
+  </si>
+  <si>
+    <t>Data sheet:</t>
+  </si>
+  <si>
+    <t>ICEV-g_Microcar_Conventinal design</t>
+  </si>
+  <si>
+    <t>wrong label: "ICEV-g_Microcar_Conventinal design" instead of "ICEV-g_Microcar_Conventional design"</t>
   </si>
 </sst>
 </file>
@@ -1600,7 +1606,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1769,6 +1775,15 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1811,12 +1826,13 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Komma" xfId="3" builtinId="3"/>
@@ -3049,32 +3065,32 @@
       <c r="H1" s="11"/>
     </row>
     <row r="2" spans="1:12" ht="15.6">
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="122" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2" s="123"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="106" t="s">
+        <v>371</v>
+      </c>
+      <c r="F2" s="122" t="s">
         <v>209</v>
       </c>
-      <c r="C2" s="118"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="106" t="s">
-        <v>372</v>
-      </c>
-      <c r="F2" s="117" t="s">
-        <v>210</v>
-      </c>
-      <c r="G2" s="118"/>
-      <c r="H2" s="118"/>
-      <c r="I2" s="118"/>
-      <c r="J2" s="118"/>
-      <c r="K2" s="119"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="123"/>
+      <c r="K2" s="124"/>
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="39"/>
       <c r="B3" s="40"/>
       <c r="C3" s="41" t="s">
+        <v>210</v>
+      </c>
+      <c r="D3" s="42" t="s">
         <v>211</v>
-      </c>
-      <c r="D3" s="42" t="s">
-        <v>212</v>
       </c>
       <c r="E3" s="107"/>
       <c r="L3" s="1"/>
@@ -3083,20 +3099,20 @@
       <c r="A4" s="39">
         <v>1</v>
       </c>
-      <c r="B4" s="120" t="s">
+      <c r="B4" s="125" t="s">
+        <v>212</v>
+      </c>
+      <c r="C4" s="43" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="D4" s="44" t="s">
         <v>214</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="E4" s="107" t="s">
+        <v>332</v>
+      </c>
+      <c r="F4" s="45" t="s">
         <v>215</v>
-      </c>
-      <c r="E4" s="107" t="s">
-        <v>333</v>
-      </c>
-      <c r="F4" s="45" t="s">
-        <v>216</v>
       </c>
       <c r="G4" s="46"/>
       <c r="H4" s="46"/>
@@ -3109,15 +3125,15 @@
       <c r="A5" s="39">
         <v>2</v>
       </c>
-      <c r="B5" s="121"/>
+      <c r="B5" s="126"/>
       <c r="C5" s="47" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D5" s="97" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E5" s="107" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F5" s="103" t="s">
         <v>3</v>
@@ -3135,25 +3151,25 @@
       </c>
       <c r="B6" s="51"/>
       <c r="C6" s="47" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D6" s="97" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="107" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F6" s="52" t="s">
         <v>0</v>
       </c>
       <c r="G6" s="53" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H6" s="54" t="s">
+        <v>299</v>
+      </c>
+      <c r="I6" s="54" t="s">
         <v>300</v>
-      </c>
-      <c r="I6" s="54" t="s">
-        <v>301</v>
       </c>
       <c r="J6" s="49"/>
       <c r="K6" s="78"/>
@@ -3163,29 +3179,29 @@
       <c r="A7" s="39">
         <v>4</v>
       </c>
-      <c r="B7" s="122" t="s">
+      <c r="B7" s="127" t="s">
+        <v>220</v>
+      </c>
+      <c r="C7" s="47" t="s">
         <v>221</v>
       </c>
-      <c r="C7" s="47" t="s">
-        <v>222</v>
-      </c>
       <c r="D7" s="48" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E7" s="107" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F7" s="52" t="s">
         <v>1</v>
       </c>
       <c r="G7" s="79" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H7" s="80" t="s">
         <v>124</v>
       </c>
       <c r="I7" s="80" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J7" s="49"/>
       <c r="K7" s="78"/>
@@ -3195,21 +3211,21 @@
       <c r="A8" s="39">
         <v>5</v>
       </c>
-      <c r="B8" s="122"/>
+      <c r="B8" s="127"/>
       <c r="C8" s="47" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D8" s="98">
         <v>3</v>
       </c>
       <c r="E8" s="107" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F8" s="52" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="79" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H8" s="55" t="s">
         <v>9</v>
@@ -3223,21 +3239,21 @@
       <c r="A9" s="39">
         <v>6</v>
       </c>
-      <c r="B9" s="122"/>
+      <c r="B9" s="127"/>
       <c r="C9" s="47" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D9" s="98" t="s">
         <v>103</v>
       </c>
       <c r="E9" s="107" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F9" s="52" t="s">
         <v>5</v>
       </c>
       <c r="G9" s="79" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H9" s="55" t="s">
         <v>9</v>
@@ -3251,15 +3267,15 @@
       <c r="A10" s="39">
         <v>7</v>
       </c>
-      <c r="B10" s="122"/>
+      <c r="B10" s="127"/>
       <c r="C10" s="47" t="s">
-        <v>225</v>
-      </c>
-      <c r="D10" s="126" t="s">
-        <v>379</v>
+        <v>224</v>
+      </c>
+      <c r="D10" s="112" t="s">
+        <v>378</v>
       </c>
       <c r="E10" s="107" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F10" s="57" t="s">
         <v>2</v>
@@ -3285,29 +3301,29 @@
       <c r="A11" s="39">
         <v>8</v>
       </c>
-      <c r="B11" s="123" t="s">
+      <c r="B11" s="128" t="s">
+        <v>225</v>
+      </c>
+      <c r="C11" s="61" t="s">
         <v>226</v>
-      </c>
-      <c r="C11" s="61" t="s">
-        <v>227</v>
       </c>
       <c r="D11" s="97" t="s">
         <v>9</v>
       </c>
       <c r="E11" s="107" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F11" s="57" t="s">
         <v>12</v>
       </c>
       <c r="G11" s="81" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H11" s="81" t="s">
         <v>13</v>
       </c>
       <c r="I11" s="81" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J11" s="81" t="s">
         <v>6</v>
@@ -3321,33 +3337,33 @@
       <c r="A12" s="39">
         <v>9</v>
       </c>
-      <c r="B12" s="124"/>
+      <c r="B12" s="129"/>
       <c r="C12" s="62" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D12" s="97" t="s">
         <v>9</v>
       </c>
       <c r="E12" s="107" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F12" s="64" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G12" s="83">
         <v>1</v>
       </c>
       <c r="H12" s="79" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I12" s="83">
         <v>1</v>
       </c>
       <c r="J12" s="79" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K12" s="56" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L12" s="1"/>
     </row>
@@ -3355,18 +3371,18 @@
       <c r="A13" s="39">
         <v>10</v>
       </c>
-      <c r="B13" s="124"/>
+      <c r="B13" s="129"/>
       <c r="C13" s="62" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D13" s="97" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E13" s="107" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F13" s="64" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G13" s="90">
         <v>1</v>
@@ -3385,15 +3401,15 @@
       <c r="A14" s="39">
         <v>11</v>
       </c>
-      <c r="B14" s="124"/>
+      <c r="B14" s="129"/>
       <c r="C14" s="62" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D14" s="97" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E14" s="107" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F14" s="64" t="s">
         <v>16</v>
@@ -3411,15 +3427,15 @@
       <c r="A15" s="39">
         <v>12</v>
       </c>
-      <c r="B15" s="124"/>
+      <c r="B15" s="129"/>
       <c r="C15" s="62" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D15" s="97" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E15" s="107" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F15" s="104" t="s">
         <v>3</v>
@@ -3435,15 +3451,15 @@
       <c r="A16" s="39">
         <v>13</v>
       </c>
-      <c r="B16" s="124"/>
+      <c r="B16" s="129"/>
       <c r="C16" s="62" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D16" s="97" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E16" s="107" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F16" s="104" t="s">
         <v>3</v>
@@ -3459,15 +3475,15 @@
       <c r="A17" s="39">
         <v>14</v>
       </c>
-      <c r="B17" s="124"/>
+      <c r="B17" s="129"/>
       <c r="C17" s="62" t="s">
+        <v>236</v>
+      </c>
+      <c r="D17" s="97" t="s">
         <v>237</v>
       </c>
-      <c r="D17" s="97" t="s">
-        <v>238</v>
-      </c>
       <c r="E17" s="107" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F17" s="104" t="s">
         <v>3</v>
@@ -3483,15 +3499,15 @@
       <c r="A18" s="39">
         <v>15</v>
       </c>
-      <c r="B18" s="124"/>
+      <c r="B18" s="129"/>
       <c r="C18" s="62" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D18" s="97" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F18" s="104" t="s">
         <v>3</v>
@@ -3507,15 +3523,15 @@
       <c r="A19" s="39">
         <v>16</v>
       </c>
-      <c r="B19" s="124"/>
+      <c r="B19" s="129"/>
       <c r="C19" s="62" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D19" s="97" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E19" s="107" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F19" s="104" t="s">
         <v>3</v>
@@ -3531,15 +3547,15 @@
       <c r="A20" s="39">
         <v>17</v>
       </c>
-      <c r="B20" s="124"/>
+      <c r="B20" s="129"/>
       <c r="C20" s="62" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D20" s="97" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E20" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F20" s="104" t="s">
         <v>3</v>
@@ -3555,17 +3571,17 @@
       <c r="A21" s="39">
         <v>18</v>
       </c>
-      <c r="B21" s="125" t="s">
+      <c r="B21" s="130" t="s">
+        <v>241</v>
+      </c>
+      <c r="C21" s="62" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="62" t="s">
-        <v>243</v>
-      </c>
       <c r="D21" s="97" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E21" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F21" s="105" t="s">
         <v>3</v>
@@ -3581,15 +3597,15 @@
       <c r="A22" s="39">
         <v>19</v>
       </c>
-      <c r="B22" s="125"/>
+      <c r="B22" s="130"/>
       <c r="C22" s="62" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D22" s="97" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E22" s="107" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>3</v>
@@ -3602,15 +3618,15 @@
       <c r="A23" s="39">
         <v>20</v>
       </c>
-      <c r="B23" s="125"/>
+      <c r="B23" s="130"/>
       <c r="C23" s="61" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D23" s="98" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E23" s="107" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>3</v>
@@ -3623,15 +3639,15 @@
       <c r="A24" s="39">
         <v>21</v>
       </c>
-      <c r="B24" s="125"/>
+      <c r="B24" s="130"/>
       <c r="C24" s="61" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D24" s="99">
         <v>384</v>
       </c>
       <c r="E24" s="107" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>3</v>
@@ -3644,15 +3660,15 @@
       <c r="A25" s="39">
         <v>22</v>
       </c>
-      <c r="B25" s="125"/>
+      <c r="B25" s="130"/>
       <c r="C25" s="62" t="s">
         <v>14</v>
       </c>
       <c r="D25" s="97" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E25" s="107" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>3</v>
@@ -3665,17 +3681,17 @@
       <c r="A26" s="39">
         <v>23</v>
       </c>
-      <c r="B26" s="112" t="s">
+      <c r="B26" s="117" t="s">
+        <v>246</v>
+      </c>
+      <c r="C26" s="70" t="s">
         <v>247</v>
       </c>
-      <c r="C26" s="70" t="s">
-        <v>248</v>
-      </c>
       <c r="D26" s="98" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E26" s="107" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>3</v>
@@ -3688,15 +3704,15 @@
       <c r="A27" s="39">
         <v>24</v>
       </c>
-      <c r="B27" s="112"/>
+      <c r="B27" s="117"/>
       <c r="C27" s="70" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D27" s="98">
         <v>7</v>
       </c>
       <c r="E27" s="107" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>3</v>
@@ -3711,12 +3727,12 @@
       <c r="A28" s="39">
         <v>25</v>
       </c>
-      <c r="B28" s="112"/>
+      <c r="B28" s="117"/>
       <c r="C28" s="70" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D28" s="98" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E28" s="107" t="s">
         <v>3</v>
@@ -3734,9 +3750,9 @@
       <c r="A29" s="39">
         <v>26</v>
       </c>
-      <c r="B29" s="112"/>
+      <c r="B29" s="117"/>
       <c r="C29" s="70" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D29" s="100">
         <v>2</v>
@@ -3745,7 +3761,7 @@
         <v>3</v>
       </c>
       <c r="F29" s="109" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H29" s="9"/>
       <c r="I29" s="9"/>
@@ -3769,9 +3785,9 @@
       <c r="A30" s="39">
         <v>27</v>
       </c>
-      <c r="B30" s="112"/>
+      <c r="B30" s="117"/>
       <c r="C30" s="70" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D30" s="98" t="s">
         <v>16</v>
@@ -3780,12 +3796,13 @@
         <v>3</v>
       </c>
       <c r="F30" s="110" t="s">
-        <v>374</v>
-      </c>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
+        <v>373</v>
+      </c>
+      <c r="G30" s="131"/>
+      <c r="H30" s="132"/>
+      <c r="I30" s="133"/>
+      <c r="J30" s="132"/>
+      <c r="K30" s="133"/>
       <c r="L30" s="9"/>
       <c r="R30" s="9"/>
       <c r="S30" s="9"/>
@@ -3804,9 +3821,9 @@
       <c r="A31" s="39">
         <v>28</v>
       </c>
-      <c r="B31" s="112"/>
+      <c r="B31" s="117"/>
       <c r="C31" s="70" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D31" s="98">
         <v>14</v>
@@ -3815,12 +3832,13 @@
         <v>3</v>
       </c>
       <c r="F31" s="111" t="s">
-        <v>375</v>
-      </c>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
+        <v>374</v>
+      </c>
+      <c r="G31" s="134"/>
+      <c r="H31" s="135"/>
+      <c r="I31" s="136"/>
+      <c r="J31" s="135"/>
+      <c r="K31" s="136"/>
       <c r="L31" s="9"/>
       <c r="R31" s="9"/>
       <c r="S31" s="9"/>
@@ -3839,15 +3857,15 @@
       <c r="A32" s="39">
         <v>29</v>
       </c>
-      <c r="B32" s="112"/>
+      <c r="B32" s="117"/>
       <c r="C32" s="70" t="s">
-        <v>254</v>
-      </c>
-      <c r="D32" s="126" t="s">
-        <v>377</v>
+        <v>253</v>
+      </c>
+      <c r="D32" s="112" t="s">
+        <v>376</v>
       </c>
       <c r="E32" s="107" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>3</v>
@@ -3874,9 +3892,9 @@
       <c r="A33" s="39">
         <v>30</v>
       </c>
-      <c r="B33" s="112"/>
+      <c r="B33" s="117"/>
       <c r="C33" s="70" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D33" s="98">
         <v>4</v>
@@ -3884,8 +3902,8 @@
       <c r="E33" s="107" t="s">
         <v>3</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>3</v>
+      <c r="F33" s="114" t="s">
+        <v>381</v>
       </c>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
@@ -3910,9 +3928,9 @@
       <c r="A34" s="39">
         <v>31</v>
       </c>
-      <c r="B34" s="112"/>
+      <c r="B34" s="117"/>
       <c r="C34" s="70" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D34" s="100" t="s">
         <v>9</v>
@@ -3920,14 +3938,14 @@
       <c r="E34" s="107" t="s">
         <v>3</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
+      <c r="F34" s="115" t="s">
+        <v>383</v>
+      </c>
+      <c r="G34" s="137"/>
+      <c r="H34" s="137"/>
+      <c r="I34" s="137"/>
+      <c r="J34" s="137"/>
+      <c r="K34" s="137"/>
       <c r="L34" s="9"/>
       <c r="R34" s="9"/>
       <c r="S34" s="9"/>
@@ -3946,9 +3964,9 @@
       <c r="A35" s="39">
         <v>32</v>
       </c>
-      <c r="B35" s="112"/>
+      <c r="B35" s="117"/>
       <c r="C35" s="70" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D35" s="100" t="s">
         <v>9</v>
@@ -3982,9 +4000,9 @@
       <c r="A36" s="39">
         <v>33</v>
       </c>
-      <c r="B36" s="112"/>
+      <c r="B36" s="117"/>
       <c r="C36" s="70" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D36" s="98" t="s">
         <v>9</v>
@@ -4018,9 +4036,9 @@
       <c r="A37" s="39">
         <v>34</v>
       </c>
-      <c r="B37" s="112"/>
+      <c r="B37" s="117"/>
       <c r="C37" s="70" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D37" s="98" t="s">
         <v>9</v>
@@ -4048,9 +4066,9 @@
       <c r="A38" s="39">
         <v>35</v>
       </c>
-      <c r="B38" s="112"/>
+      <c r="B38" s="117"/>
       <c r="C38" s="70" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D38" s="98" t="s">
         <v>9</v>
@@ -4078,9 +4096,9 @@
       <c r="A39" s="39">
         <v>36</v>
       </c>
-      <c r="B39" s="112"/>
+      <c r="B39" s="117"/>
       <c r="C39" s="70" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D39" s="98" t="s">
         <v>9</v>
@@ -4108,9 +4126,9 @@
       <c r="A40" s="39">
         <v>37</v>
       </c>
-      <c r="B40" s="112"/>
+      <c r="B40" s="117"/>
       <c r="C40" s="70" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D40" s="98" t="s">
         <v>9</v>
@@ -4138,9 +4156,9 @@
       <c r="A41" s="39">
         <v>38</v>
       </c>
-      <c r="B41" s="112"/>
+      <c r="B41" s="117"/>
       <c r="C41" s="70" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D41" s="98" t="s">
         <v>9</v>
@@ -4168,9 +4186,9 @@
       <c r="A42" s="39">
         <v>39</v>
       </c>
-      <c r="B42" s="112"/>
+      <c r="B42" s="117"/>
       <c r="C42" s="70" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D42" s="98" t="s">
         <v>9</v>
@@ -4198,9 +4216,9 @@
       <c r="A43" s="39">
         <v>40</v>
       </c>
-      <c r="B43" s="112"/>
+      <c r="B43" s="117"/>
       <c r="C43" s="70" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D43" s="98" t="s">
         <v>9</v>
@@ -4228,9 +4246,9 @@
       <c r="A44" s="39">
         <v>41</v>
       </c>
-      <c r="B44" s="112"/>
+      <c r="B44" s="117"/>
       <c r="C44" s="70" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D44" s="98" t="s">
         <v>9</v>
@@ -4258,9 +4276,9 @@
       <c r="A45" s="39">
         <v>42</v>
       </c>
-      <c r="B45" s="112"/>
+      <c r="B45" s="117"/>
       <c r="C45" s="70" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D45" s="98" t="s">
         <v>9</v>
@@ -4288,9 +4306,9 @@
       <c r="A46" s="39">
         <v>43</v>
       </c>
-      <c r="B46" s="112"/>
+      <c r="B46" s="117"/>
       <c r="C46" s="70" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D46" s="98" t="s">
         <v>9</v>
@@ -4318,9 +4336,9 @@
       <c r="A47" s="39">
         <v>44</v>
       </c>
-      <c r="B47" s="112"/>
+      <c r="B47" s="117"/>
       <c r="C47" s="70" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D47" s="98" t="s">
         <v>9</v>
@@ -4348,9 +4366,9 @@
       <c r="A48" s="39">
         <v>45</v>
       </c>
-      <c r="B48" s="112"/>
+      <c r="B48" s="117"/>
       <c r="C48" s="70" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D48" s="98" t="s">
         <v>9</v>
@@ -4378,9 +4396,9 @@
       <c r="A49" s="39">
         <v>46</v>
       </c>
-      <c r="B49" s="112"/>
+      <c r="B49" s="117"/>
       <c r="C49" s="70" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D49" s="98" t="s">
         <v>9</v>
@@ -4408,15 +4426,15 @@
       <c r="A50" s="39">
         <v>47</v>
       </c>
-      <c r="B50" s="112"/>
+      <c r="B50" s="117"/>
       <c r="C50" s="61" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D50" s="97" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E50" s="107" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>3</v>
@@ -4438,15 +4456,15 @@
       <c r="A51" s="39">
         <v>48</v>
       </c>
-      <c r="B51" s="112"/>
+      <c r="B51" s="117"/>
       <c r="C51" s="61" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D51" s="97" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E51" s="107" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>3</v>
@@ -4468,15 +4486,15 @@
       <c r="A52" s="39">
         <v>49</v>
       </c>
-      <c r="B52" s="112"/>
+      <c r="B52" s="117"/>
       <c r="C52" s="61" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D52" s="97" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E52" s="107" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>3</v>
@@ -4498,17 +4516,17 @@
       <c r="A53" s="39">
         <v>50</v>
       </c>
-      <c r="B53" s="113" t="s">
+      <c r="B53" s="118" t="s">
+        <v>274</v>
+      </c>
+      <c r="C53" s="47" t="s">
         <v>275</v>
       </c>
-      <c r="C53" s="47" t="s">
-        <v>276</v>
-      </c>
-      <c r="D53" s="127" t="s">
-        <v>381</v>
+      <c r="D53" s="113" t="s">
+        <v>380</v>
       </c>
       <c r="E53" s="107" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>3</v>
@@ -4530,15 +4548,15 @@
       <c r="A54" s="39">
         <v>51</v>
       </c>
-      <c r="B54" s="113"/>
+      <c r="B54" s="118"/>
       <c r="C54" s="47" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D54" s="98" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E54" s="107" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>3</v>
@@ -4560,15 +4578,15 @@
       <c r="A55" s="39">
         <v>52</v>
       </c>
-      <c r="B55" s="113"/>
+      <c r="B55" s="118"/>
       <c r="C55" s="74" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D55" s="97" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E55" s="107" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>3</v>
@@ -4590,15 +4608,15 @@
       <c r="A56" s="39">
         <v>53</v>
       </c>
-      <c r="B56" s="113"/>
+      <c r="B56" s="118"/>
       <c r="C56" s="74" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D56" s="97" t="s">
         <v>9</v>
       </c>
       <c r="E56" s="107" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>3</v>
@@ -4620,15 +4638,15 @@
       <c r="A57" s="39">
         <v>54</v>
       </c>
-      <c r="B57" s="113"/>
+      <c r="B57" s="118"/>
       <c r="C57" s="62" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D57" s="97" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E57" s="107" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>3</v>
@@ -4650,15 +4668,15 @@
       <c r="A58" s="39">
         <v>55</v>
       </c>
-      <c r="B58" s="113"/>
+      <c r="B58" s="118"/>
       <c r="C58" s="74" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D58" s="97" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E58" s="107" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>3</v>
@@ -4680,15 +4698,15 @@
       <c r="A59" s="39">
         <v>56</v>
       </c>
-      <c r="B59" s="113"/>
+      <c r="B59" s="118"/>
       <c r="C59" s="74" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D59" s="97" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E59" s="107" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>3</v>
@@ -4710,15 +4728,15 @@
       <c r="A60" s="39">
         <v>57</v>
       </c>
-      <c r="B60" s="113"/>
+      <c r="B60" s="118"/>
       <c r="C60" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D60" s="101">
         <v>1</v>
       </c>
       <c r="E60" s="107" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>3</v>
@@ -4740,17 +4758,17 @@
       <c r="A61" s="39">
         <v>58</v>
       </c>
-      <c r="B61" s="114" t="s">
+      <c r="B61" s="119" t="s">
+        <v>283</v>
+      </c>
+      <c r="C61" s="74" t="s">
         <v>284</v>
-      </c>
-      <c r="C61" s="74" t="s">
-        <v>285</v>
       </c>
       <c r="D61" s="102">
         <v>43684</v>
       </c>
       <c r="E61" s="107" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>3</v>
@@ -4772,15 +4790,15 @@
       <c r="A62" s="39">
         <v>59</v>
       </c>
-      <c r="B62" s="114"/>
+      <c r="B62" s="119"/>
       <c r="C62" s="74" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D62" s="102">
         <v>45605</v>
       </c>
       <c r="E62" s="107" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>3</v>
@@ -4802,15 +4820,15 @@
       <c r="A63" s="39">
         <v>60</v>
       </c>
-      <c r="B63" s="114"/>
+      <c r="B63" s="119"/>
       <c r="C63" s="74" t="s">
+        <v>286</v>
+      </c>
+      <c r="D63" s="97" t="s">
         <v>287</v>
       </c>
-      <c r="D63" s="97" t="s">
-        <v>288</v>
-      </c>
       <c r="E63" s="107" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>3</v>
@@ -4832,15 +4850,15 @@
       <c r="A64" s="39">
         <v>61</v>
       </c>
-      <c r="B64" s="114"/>
+      <c r="B64" s="119"/>
       <c r="C64" s="74" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D64" s="97" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E64" s="107" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>3</v>
@@ -4862,13 +4880,13 @@
       <c r="A65" s="39">
         <v>62</v>
       </c>
-      <c r="B65" s="114"/>
+      <c r="B65" s="119"/>
       <c r="C65" s="47" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D65" s="92"/>
       <c r="E65" s="107" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>3</v>
@@ -4890,13 +4908,13 @@
       <c r="A66" s="39">
         <v>63</v>
       </c>
-      <c r="B66" s="114"/>
+      <c r="B66" s="119"/>
       <c r="C66" s="47" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D66" s="92"/>
       <c r="E66" s="107" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>3</v>
@@ -4906,13 +4924,13 @@
       <c r="A67" s="39">
         <v>64</v>
       </c>
-      <c r="B67" s="114"/>
+      <c r="B67" s="119"/>
       <c r="C67" s="74" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D67" s="92"/>
       <c r="E67" s="107" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>3</v>
@@ -4922,11 +4940,11 @@
       <c r="A68" s="39">
         <v>65</v>
       </c>
-      <c r="B68" s="115" t="s">
+      <c r="B68" s="120" t="s">
+        <v>292</v>
+      </c>
+      <c r="C68" s="75" t="s">
         <v>293</v>
-      </c>
-      <c r="C68" s="75" t="s">
-        <v>294</v>
       </c>
       <c r="D68" s="50"/>
       <c r="E68" s="107" t="s">
@@ -4937,9 +4955,9 @@
       <c r="A69" s="39">
         <v>66</v>
       </c>
-      <c r="B69" s="115"/>
+      <c r="B69" s="120"/>
       <c r="C69" s="75" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D69" s="50"/>
       <c r="E69" s="107" t="s">
@@ -4950,9 +4968,9 @@
       <c r="A70" s="39">
         <v>67</v>
       </c>
-      <c r="B70" s="115"/>
+      <c r="B70" s="120"/>
       <c r="C70" s="75" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D70" s="50"/>
       <c r="E70" s="107" t="s">
@@ -4963,9 +4981,9 @@
       <c r="A71" s="39">
         <v>68</v>
       </c>
-      <c r="B71" s="115"/>
+      <c r="B71" s="120"/>
       <c r="C71" s="75" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D71" s="50"/>
       <c r="E71" s="107" t="s">
@@ -4976,9 +4994,9 @@
       <c r="A72" s="39">
         <v>69</v>
       </c>
-      <c r="B72" s="116"/>
+      <c r="B72" s="121"/>
       <c r="C72" s="76" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D72" s="68"/>
       <c r="E72" s="107" t="s">
@@ -5043,16 +5061,16 @@
   <sheetData>
     <row r="1" spans="1:180">
       <c r="A1" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>43</v>
@@ -5061,13 +5079,13 @@
         <v>44</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>329</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>330</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>49</v>
@@ -5247,13 +5265,13 @@
     </row>
     <row r="2" spans="1:180">
       <c r="A2" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D2" s="5">
         <v>593.91318234627215</v>
@@ -5282,13 +5300,13 @@
     </row>
     <row r="3" spans="1:180">
       <c r="A3" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D3" s="5">
         <v>933.22672754179075</v>
@@ -5316,14 +5334,14 @@
       </c>
     </row>
     <row r="4" spans="1:180">
-      <c r="A4" s="4" t="s">
-        <v>158</v>
+      <c r="A4" s="116" t="s">
+        <v>382</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D4" s="5">
         <v>334.27650201447852</v>
@@ -5352,13 +5370,13 @@
     </row>
     <row r="5" spans="1:180">
       <c r="A5" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D5" s="5">
         <v>784.40499719287914</v>
@@ -5387,13 +5405,13 @@
     </row>
     <row r="6" spans="1:180">
       <c r="A6" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D6" s="5">
         <v>602.61352965897777</v>
@@ -5422,13 +5440,13 @@
     </row>
     <row r="7" spans="1:180">
       <c r="A7" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D7" s="5">
         <v>948.33785708491109</v>
@@ -5457,13 +5475,13 @@
     </row>
     <row r="8" spans="1:180">
       <c r="A8" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D8" s="5">
         <v>340.01415211069968</v>
@@ -5492,13 +5510,13 @@
     </row>
     <row r="9" spans="1:180">
       <c r="A9" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D9" s="5">
         <v>794.79962266647988</v>
@@ -5527,13 +5545,13 @@
     </row>
     <row r="10" spans="1:180">
       <c r="A10" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D10" s="5">
         <v>657.7232025847876</v>
@@ -5562,13 +5580,13 @@
     </row>
     <row r="11" spans="1:180">
       <c r="A11" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D11" s="5">
         <v>1036.0429634443196</v>
@@ -5597,13 +5615,13 @@
     </row>
     <row r="12" spans="1:180">
       <c r="A12" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D12" s="5">
         <v>377.04267804706416</v>
@@ -5632,13 +5650,13 @@
     </row>
     <row r="13" spans="1:180">
       <c r="A13" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D13" s="5">
         <v>860.74994614703633</v>
@@ -5667,13 +5685,13 @@
     </row>
     <row r="14" spans="1:180">
       <c r="A14" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D14" s="6">
         <v>628.49904328101616</v>
@@ -5702,13 +5720,13 @@
     </row>
     <row r="15" spans="1:180">
       <c r="A15" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D15" s="5">
         <v>963.38001243765996</v>
@@ -5737,13 +5755,13 @@
     </row>
     <row r="16" spans="1:180">
       <c r="A16" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D16" s="5">
         <v>364.09654955601189</v>
@@ -5772,13 +5790,13 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D17" s="5">
         <v>819.71837870465617</v>
@@ -5807,13 +5825,13 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D18" s="6">
         <v>715.98856977199068</v>
@@ -5842,13 +5860,13 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D19" s="6">
         <v>1091.7467275215645</v>
@@ -5877,13 +5895,13 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D20" s="6">
         <v>436.27112796395073</v>
@@ -5912,13 +5930,13 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D21" s="6">
         <v>914.22248267020473</v>
@@ -5947,13 +5965,13 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D22" s="6">
         <v>608.07655530953593</v>
@@ -5982,13 +6000,13 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D23" s="6">
         <v>944.37750332682663</v>
@@ -6017,13 +6035,13 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D24" s="6">
         <v>349.21491895003936</v>
@@ -6052,13 +6070,13 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D25" s="6">
         <v>818.37345634689098</v>
@@ -6087,13 +6105,13 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D26" s="6">
         <v>240.75327503067197</v>
@@ -6122,13 +6140,13 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D27" s="6">
         <v>378.11295191152561</v>
@@ -6157,13 +6175,13 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D28" s="6">
         <v>127.65661992530642</v>
@@ -6192,13 +6210,13 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D29" s="6">
         <v>300.11515923329819</v>
@@ -6227,13 +6245,13 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D30" s="5">
         <v>244.17124521744279</v>
@@ -6262,13 +6280,13 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D31" s="5">
         <v>384.09439973837459</v>
@@ -6297,13 +6315,13 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D32" s="5">
         <v>129.80533916655028</v>
@@ -6332,13 +6350,13 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D33" s="5">
         <v>304.00789081958976</v>
@@ -6367,13 +6385,13 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D34" s="5">
         <v>270.24549809265579</v>
@@ -6402,13 +6420,13 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D35" s="5">
         <v>425.67636811236127</v>
@@ -6437,13 +6455,13 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D36" s="5">
         <v>144.12427643694232</v>
@@ -6472,13 +6490,13 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D37" s="5">
         <v>329.89630188133083</v>
@@ -6507,13 +6525,13 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D38" s="5">
         <v>256.16696552462736</v>
@@ -6542,13 +6560,13 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D39" s="5">
         <v>392.33545218223657</v>
@@ -6577,13 +6595,13 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D40" s="5">
         <v>136.45275914969753</v>
@@ -6612,13 +6630,13 @@
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D41" s="5">
         <v>308.21999836191435</v>
@@ -6647,13 +6665,13 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D42" s="5">
         <v>182.73595307676916</v>
@@ -6682,13 +6700,13 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D43" s="5">
         <v>278.55160580269677</v>
@@ -6717,13 +6735,13 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D44" s="5">
         <v>102.46367388307539</v>
@@ -6752,13 +6770,13 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D45" s="5">
         <v>215.57413474998822</v>
@@ -6787,13 +6805,13 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D46" s="5">
         <v>166.1086239340479</v>
@@ -6822,13 +6840,13 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D47" s="5">
         <v>257.89067715862353</v>
@@ -6857,13 +6875,13 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D48" s="5">
         <v>87.650530563898869</v>
@@ -6892,13 +6910,13 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D49" s="5">
         <v>205.89191681802956</v>
@@ -22980,10 +22998,10 @@
         <v>85</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>86</v>
@@ -23030,7 +23048,7 @@
         <v>97</v>
       </c>
       <c r="P3" s="38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
